--- a/informes_data/Segunda FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486992_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Segunda FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486992_PROCESSED_CHRONO.xlsx
@@ -553,7 +553,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>M. ABDULSALAM</t>
+          <t>J. NVE MALEVA</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -565,73 +565,73 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>5.5052</v>
+        <v>4.0048</v>
       </c>
       <c r="E2" t="n">
-        <v>2.7755</v>
+        <v>3.2851</v>
       </c>
       <c r="F2" t="n">
-        <v>2.7297</v>
+        <v>0.7197</v>
       </c>
       <c r="G2" t="n">
-        <v>1.1501</v>
+        <v>3.1979</v>
       </c>
       <c r="H2" t="n">
-        <v>1.713</v>
+        <v>3.1239</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.5629</v>
+        <v>0.07389999999999999</v>
       </c>
       <c r="J2" t="n">
-        <v>3.483</v>
+        <v>3.5444</v>
       </c>
       <c r="K2" t="n">
-        <v>2.6542</v>
+        <v>3.426</v>
       </c>
       <c r="L2" t="n">
-        <v>0.8288</v>
+        <v>0.1184</v>
       </c>
       <c r="M2" t="n">
-        <v>-2.3328</v>
+        <v>-0.3465</v>
       </c>
       <c r="N2" t="n">
-        <v>-0.9412</v>
+        <v>-0.302</v>
       </c>
       <c r="O2" t="n">
-        <v>-1.3917</v>
+        <v>-0.0445</v>
       </c>
       <c r="P2" t="n">
-        <v>-1.0267</v>
+        <v>-0.4107</v>
       </c>
       <c r="Q2" t="n">
-        <v>-3.2855</v>
+        <v>-1.6427</v>
       </c>
       <c r="R2" t="n">
-        <v>2.2588</v>
+        <v>1.2321</v>
       </c>
       <c r="S2" t="n">
-        <v>1.9773</v>
+        <v>0.9774</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.0195</v>
+        <v>0.5538999999999999</v>
       </c>
       <c r="U2" t="n">
-        <v>1.9968</v>
+        <v>0.4235</v>
       </c>
       <c r="V2" t="n">
-        <v>3.4045</v>
+        <v>0.2402</v>
       </c>
       <c r="W2" t="n">
-        <v>2.5975</v>
+        <v>0.8295</v>
       </c>
       <c r="X2" t="n">
-        <v>0.8070000000000001</v>
+        <v>-0.5893</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>J. NVE MALEVA</t>
+          <t>M. ABDULSALAM</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,67 +643,67 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>4.928</v>
+        <v>3.99</v>
       </c>
       <c r="E3" t="n">
-        <v>3.4672</v>
+        <v>2.3571</v>
       </c>
       <c r="F3" t="n">
-        <v>1.4608</v>
+        <v>1.633</v>
       </c>
       <c r="G3" t="n">
-        <v>3.1979</v>
+        <v>1.1501</v>
       </c>
       <c r="H3" t="n">
-        <v>3.1239</v>
+        <v>1.713</v>
       </c>
       <c r="I3" t="n">
-        <v>0.07389999999999999</v>
+        <v>-0.5629</v>
       </c>
       <c r="J3" t="n">
-        <v>3.5444</v>
+        <v>3.483</v>
       </c>
       <c r="K3" t="n">
-        <v>3.426</v>
+        <v>2.6542</v>
       </c>
       <c r="L3" t="n">
-        <v>0.1184</v>
+        <v>0.8288</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.3465</v>
+        <v>-2.3328</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.302</v>
+        <v>-0.9412</v>
       </c>
       <c r="O3" t="n">
-        <v>-0.0445</v>
+        <v>-1.3917</v>
       </c>
       <c r="P3" t="n">
-        <v>-0.4107</v>
+        <v>-1.0267</v>
       </c>
       <c r="Q3" t="n">
-        <v>-1.6427</v>
+        <v>-3.2855</v>
       </c>
       <c r="R3" t="n">
-        <v>1.2321</v>
+        <v>2.2588</v>
       </c>
       <c r="S3" t="n">
-        <v>1.9005</v>
+        <v>0.4621</v>
       </c>
       <c r="T3" t="n">
-        <v>0.736</v>
+        <v>-0.4379</v>
       </c>
       <c r="U3" t="n">
-        <v>1.1645</v>
+        <v>0.9</v>
       </c>
       <c r="V3" t="n">
-        <v>0.2402</v>
+        <v>3.4045</v>
       </c>
       <c r="W3" t="n">
-        <v>0.8295</v>
+        <v>2.5975</v>
       </c>
       <c r="X3" t="n">
-        <v>-0.5893</v>
+        <v>0.8070000000000001</v>
       </c>
     </row>
     <row r="4">
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>1.7131</v>
+        <v>2.4558</v>
       </c>
       <c r="E4" t="n">
-        <v>0.2901</v>
+        <v>0.4993</v>
       </c>
       <c r="F4" t="n">
-        <v>1.423</v>
+        <v>1.9565</v>
       </c>
       <c r="G4" t="n">
         <v>1.3337</v>
@@ -766,13 +766,13 @@
         <v>2.6694</v>
       </c>
       <c r="S4" t="n">
-        <v>-1.6823</v>
+        <v>-0.9395</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.9145</v>
+        <v>-0.7053</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.7678</v>
+        <v>-0.2342</v>
       </c>
       <c r="V4" t="n">
         <v>0.8295</v>
@@ -787,7 +787,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>E. ORTIZ TORRES</t>
+          <t>C. HENDERSON</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>1.2627</v>
+        <v>1.9936</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.0622</v>
+        <v>2.0129</v>
       </c>
       <c r="F5" t="n">
-        <v>1.3249</v>
+        <v>-0.0193</v>
       </c>
       <c r="G5" t="n">
-        <v>0.9035</v>
+        <v>1.864</v>
       </c>
       <c r="H5" t="n">
-        <v>-1.9855</v>
+        <v>1.4694</v>
       </c>
       <c r="I5" t="n">
-        <v>2.889</v>
+        <v>0.3947</v>
       </c>
       <c r="J5" t="n">
-        <v>1.6892</v>
+        <v>4.7019</v>
       </c>
       <c r="K5" t="n">
-        <v>-0.8497</v>
+        <v>2.9393</v>
       </c>
       <c r="L5" t="n">
-        <v>2.5388</v>
+        <v>1.7626</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.7856</v>
+        <v>-2.8379</v>
       </c>
       <c r="N5" t="n">
-        <v>-1.1358</v>
+        <v>-1.47</v>
       </c>
       <c r="O5" t="n">
-        <v>0.3502</v>
+        <v>-1.3679</v>
       </c>
       <c r="P5" t="n">
         <v>-0.2053</v>
       </c>
       <c r="Q5" t="n">
-        <v>-2.4641</v>
+        <v>-2.2588</v>
       </c>
       <c r="R5" t="n">
-        <v>2.2588</v>
+        <v>2.0534</v>
       </c>
       <c r="S5" t="n">
-        <v>0.5645</v>
+        <v>-0.123</v>
       </c>
       <c r="T5" t="n">
-        <v>0.4725</v>
+        <v>-0.4302</v>
       </c>
       <c r="U5" t="n">
-        <v>0.092</v>
+        <v>0.3072</v>
       </c>
       <c r="V5" t="n">
+        <v>0.4579</v>
+      </c>
+      <c r="W5" t="n">
         <v>0</v>
       </c>
-      <c r="W5" t="n">
-        <v>0.2402</v>
-      </c>
       <c r="X5" t="n">
-        <v>-0.2402</v>
+        <v>0.4579</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>C. HENDERSON</t>
+          <t>E. ORTIZ TORRES</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,67 +877,67 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>1.2491</v>
+        <v>1.2222</v>
       </c>
       <c r="E6" t="n">
-        <v>1.5945</v>
+        <v>-0.3101</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.3454</v>
+        <v>1.5323</v>
       </c>
       <c r="G6" t="n">
-        <v>1.864</v>
+        <v>0.9035</v>
       </c>
       <c r="H6" t="n">
-        <v>1.4694</v>
+        <v>-1.9855</v>
       </c>
       <c r="I6" t="n">
-        <v>0.3947</v>
+        <v>2.889</v>
       </c>
       <c r="J6" t="n">
-        <v>4.7019</v>
+        <v>1.6892</v>
       </c>
       <c r="K6" t="n">
-        <v>2.9393</v>
+        <v>-0.8497</v>
       </c>
       <c r="L6" t="n">
-        <v>1.7626</v>
+        <v>2.5388</v>
       </c>
       <c r="M6" t="n">
-        <v>-2.8379</v>
+        <v>-0.7856</v>
       </c>
       <c r="N6" t="n">
-        <v>-1.47</v>
+        <v>-1.1358</v>
       </c>
       <c r="O6" t="n">
-        <v>-1.3679</v>
+        <v>0.3502</v>
       </c>
       <c r="P6" t="n">
         <v>-0.2053</v>
       </c>
       <c r="Q6" t="n">
-        <v>-2.2588</v>
+        <v>-2.4641</v>
       </c>
       <c r="R6" t="n">
-        <v>2.0534</v>
+        <v>2.2588</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.8675</v>
+        <v>0.524</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.8486</v>
+        <v>0.2246</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.0189</v>
+        <v>0.2995</v>
       </c>
       <c r="V6" t="n">
-        <v>0.4579</v>
+        <v>0</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>0.2402</v>
       </c>
       <c r="X6" t="n">
-        <v>0.4579</v>
+        <v>-0.2402</v>
       </c>
     </row>
     <row r="7">
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.0345</v>
+        <v>0.09379999999999999</v>
       </c>
       <c r="E7" t="n">
         <v>1.2626</v>
       </c>
       <c r="F7" t="n">
-        <v>-1.2281</v>
+        <v>-1.1688</v>
       </c>
       <c r="G7" t="n">
         <v>-0.4234</v>
@@ -1000,13 +1000,13 @@
         <v>0.616</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.1581</v>
+        <v>-0.0988</v>
       </c>
       <c r="T7" t="n">
         <v>-0.0581</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.0999</v>
+        <v>-0.0407</v>
       </c>
       <c r="V7" t="n">
         <v>0</v>
@@ -1021,7 +1021,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>G. KASANZI OBAMA</t>
+          <t>M. ALVAREZ PUERTAS</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.3291</v>
+        <v>-0.2013</v>
       </c>
       <c r="E8" t="n">
-        <v>-1.1671</v>
+        <v>-1.4962</v>
       </c>
       <c r="F8" t="n">
-        <v>0.8379</v>
+        <v>1.2948</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.0517</v>
+        <v>-0.0466</v>
       </c>
       <c r="H8" t="n">
-        <v>0.8111</v>
+        <v>-0.1363</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.8629</v>
+        <v>0.0897</v>
       </c>
       <c r="J8" t="n">
-        <v>-0.09760000000000001</v>
+        <v>-0.2052</v>
       </c>
       <c r="K8" t="n">
-        <v>1.1393</v>
+        <v>-0.363</v>
       </c>
       <c r="L8" t="n">
-        <v>-1.2368</v>
+        <v>0.1579</v>
       </c>
       <c r="M8" t="n">
-        <v>0.0458</v>
+        <v>0.1585</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.3281</v>
+        <v>0.2268</v>
       </c>
       <c r="O8" t="n">
-        <v>0.374</v>
+        <v>-0.0682</v>
       </c>
       <c r="P8" t="n">
-        <v>0.2053</v>
+        <v>0.8214</v>
       </c>
       <c r="Q8" t="n">
-        <v>-1.8481</v>
+        <v>-0.616</v>
       </c>
       <c r="R8" t="n">
-        <v>2.0534</v>
+        <v>1.4374</v>
       </c>
       <c r="S8" t="n">
-        <v>0.4557</v>
+        <v>-0.2779</v>
       </c>
       <c r="T8" t="n">
-        <v>0.5384</v>
+        <v>0.0232</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.0827</v>
+        <v>-0.3011</v>
       </c>
       <c r="V8" t="n">
-        <v>-0.9384</v>
+        <v>-0.6982</v>
       </c>
       <c r="W8" t="n">
-        <v>0.2402</v>
+        <v>-0.6982</v>
       </c>
       <c r="X8" t="n">
-        <v>-1.1786</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>M. ALVAREZ PUERTAS</t>
+          <t>G. KASANZI OBAMA</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,67 +1111,67 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.959</v>
+        <v>-0.2288</v>
       </c>
       <c r="E9" t="n">
-        <v>-2.0463</v>
+        <v>-1.2445</v>
       </c>
       <c r="F9" t="n">
-        <v>1.0873</v>
+        <v>1.0158</v>
       </c>
       <c r="G9" t="n">
-        <v>-0.0466</v>
+        <v>-0.0517</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.1363</v>
+        <v>0.8111</v>
       </c>
       <c r="I9" t="n">
-        <v>0.0897</v>
+        <v>-0.8629</v>
       </c>
       <c r="J9" t="n">
-        <v>-0.2052</v>
+        <v>-0.09760000000000001</v>
       </c>
       <c r="K9" t="n">
-        <v>-0.363</v>
+        <v>1.1393</v>
       </c>
       <c r="L9" t="n">
-        <v>0.1579</v>
+        <v>-1.2368</v>
       </c>
       <c r="M9" t="n">
-        <v>0.1585</v>
+        <v>0.0458</v>
       </c>
       <c r="N9" t="n">
-        <v>0.2268</v>
+        <v>-0.3281</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.0682</v>
+        <v>0.374</v>
       </c>
       <c r="P9" t="n">
-        <v>0.8214</v>
+        <v>0.2053</v>
       </c>
       <c r="Q9" t="n">
-        <v>-0.616</v>
+        <v>-1.8481</v>
       </c>
       <c r="R9" t="n">
-        <v>1.4374</v>
+        <v>2.0534</v>
       </c>
       <c r="S9" t="n">
-        <v>-1.0356</v>
+        <v>0.556</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.527</v>
+        <v>0.4609</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.5086000000000001</v>
+        <v>0.0951</v>
       </c>
       <c r="V9" t="n">
-        <v>-0.6982</v>
+        <v>-0.9384</v>
       </c>
       <c r="W9" t="n">
-        <v>-0.6982</v>
+        <v>0.2402</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>-1.1786</v>
       </c>
     </row>
     <row r="10">
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-1.5045</v>
+        <v>-1.1199</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.83</v>
+        <v>-0.5937</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.6744</v>
+        <v>-0.5262</v>
       </c>
       <c r="G10" t="n">
         <v>-2.7036</v>
@@ -1234,13 +1234,13 @@
         <v>1.6427</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.0329</v>
+        <v>0.3516</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.159</v>
+        <v>0.0774</v>
       </c>
       <c r="U10" t="n">
-        <v>0.126</v>
+        <v>0.2743</v>
       </c>
       <c r="V10" t="n">
         <v>0</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-2.8257</v>
+        <v>-2.4773</v>
       </c>
       <c r="E11" t="n">
-        <v>0.6223</v>
+        <v>0.7927999999999999</v>
       </c>
       <c r="F11" t="n">
-        <v>-3.448</v>
+        <v>-3.2702</v>
       </c>
       <c r="G11" t="n">
         <v>-1.9094</v>
@@ -1312,13 +1312,13 @@
         <v>1.2321</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.9081</v>
+        <v>-0.5598</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.5192</v>
+        <v>-0.3488</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.3889</v>
+        <v>-0.211</v>
       </c>
       <c r="V11" t="n">
         <v>-0.8295</v>
@@ -1345,19 +1345,19 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>9.074299999999999</v>
+        <v>9.732900000000001</v>
       </c>
       <c r="E12" t="n">
-        <v>5.9066</v>
+        <v>6.565299999999999</v>
       </c>
       <c r="F12" t="n">
-        <v>3.1677</v>
+        <v>3.167599999999999</v>
       </c>
       <c r="G12" t="n">
         <v>3.314500000000001</v>
       </c>
       <c r="H12" t="n">
-        <v>4.5904</v>
+        <v>4.590400000000002</v>
       </c>
       <c r="I12" t="n">
         <v>-1.276</v>
@@ -1378,7 +1378,7 @@
         <v>-6.215999999999999</v>
       </c>
       <c r="O12" t="n">
-        <v>-7.1806</v>
+        <v>-7.180599999999999</v>
       </c>
       <c r="P12" t="n">
         <v>3.0803</v>
@@ -1390,16 +1390,16 @@
         <v>17.4541</v>
       </c>
       <c r="S12" t="n">
-        <v>0.2135000000000001</v>
+        <v>0.8721000000000002</v>
       </c>
       <c r="T12" t="n">
-        <v>-1.299</v>
+        <v>-0.6403000000000001</v>
       </c>
       <c r="U12" t="n">
-        <v>1.512499999999999</v>
+        <v>1.5126</v>
       </c>
       <c r="V12" t="n">
-        <v>2.466000000000001</v>
+        <v>2.466</v>
       </c>
       <c r="W12" t="n">
         <v>4.868300000000001</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>3.959</v>
+        <v>2.5712</v>
       </c>
       <c r="E13" t="n">
-        <v>1.853</v>
+        <v>0.7024</v>
       </c>
       <c r="F13" t="n">
-        <v>2.106</v>
+        <v>1.8689</v>
       </c>
       <c r="G13" t="n">
         <v>1.3245</v>
@@ -1468,13 +1468,13 @@
         <v>2.0534</v>
       </c>
       <c r="S13" t="n">
-        <v>2.271</v>
+        <v>0.8833</v>
       </c>
       <c r="T13" t="n">
-        <v>1.6773</v>
+        <v>0.5266999999999999</v>
       </c>
       <c r="U13" t="n">
-        <v>0.5937</v>
+        <v>0.3566</v>
       </c>
       <c r="V13" t="n">
         <v>-0.4579</v>
@@ -1489,7 +1489,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>G. VAZQUEZ VALLEJO</t>
+          <t>H. FIGUEROA ÁLVAREZ</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,73 +1501,73 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>0.6122</v>
+        <v>1.6617</v>
       </c>
       <c r="E14" t="n">
-        <v>1.4323</v>
+        <v>2.371</v>
       </c>
       <c r="F14" t="n">
-        <v>-0.8201000000000001</v>
+        <v>-0.7093</v>
       </c>
       <c r="G14" t="n">
-        <v>0.8045</v>
+        <v>0.09669999999999999</v>
       </c>
       <c r="H14" t="n">
-        <v>0.8467</v>
+        <v>1.7389</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.0421</v>
+        <v>-1.6422</v>
       </c>
       <c r="J14" t="n">
-        <v>3.3581</v>
+        <v>2.7345</v>
       </c>
       <c r="K14" t="n">
-        <v>2.1481</v>
+        <v>2.9851</v>
       </c>
       <c r="L14" t="n">
-        <v>1.21</v>
+        <v>-0.2506</v>
       </c>
       <c r="M14" t="n">
-        <v>-2.5536</v>
+        <v>-2.6379</v>
       </c>
       <c r="N14" t="n">
-        <v>-1.3014</v>
+        <v>-1.2462</v>
       </c>
       <c r="O14" t="n">
-        <v>-1.2522</v>
+        <v>-1.3917</v>
       </c>
       <c r="P14" t="n">
-        <v>-1.0267</v>
+        <v>-0</v>
       </c>
       <c r="Q14" t="n">
-        <v>-3.0801</v>
+        <v>-2.0534</v>
       </c>
       <c r="R14" t="n">
         <v>2.0534</v>
       </c>
       <c r="S14" t="n">
-        <v>1.5551</v>
+        <v>0.1462</v>
       </c>
       <c r="T14" t="n">
-        <v>0.9141</v>
+        <v>-0.2094</v>
       </c>
       <c r="U14" t="n">
-        <v>0.641</v>
+        <v>0.3556</v>
       </c>
       <c r="V14" t="n">
-        <v>-0.7207</v>
+        <v>1.4189</v>
       </c>
       <c r="W14" t="n">
-        <v>0.2402</v>
+        <v>1.8993</v>
       </c>
       <c r="X14" t="n">
-        <v>-0.9609</v>
+        <v>-0.4805</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A. SMITH</t>
+          <t>O. THIAM PEDRERA</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,73 +1579,73 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>0.5978</v>
+        <v>0.7416</v>
       </c>
       <c r="E15" t="n">
-        <v>0.9258999999999999</v>
+        <v>0.6299</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.3281</v>
+        <v>0.1117</v>
       </c>
       <c r="G15" t="n">
-        <v>-1.2847</v>
+        <v>0.8419</v>
       </c>
       <c r="H15" t="n">
-        <v>-0.7294</v>
+        <v>-1.421</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.5552</v>
+        <v>2.263</v>
       </c>
       <c r="J15" t="n">
-        <v>0.1194</v>
+        <v>2.0751</v>
       </c>
       <c r="K15" t="n">
-        <v>0.2117</v>
+        <v>0.0229</v>
       </c>
       <c r="L15" t="n">
-        <v>-0.09229999999999999</v>
+        <v>2.0522</v>
       </c>
       <c r="M15" t="n">
-        <v>-1.4041</v>
+        <v>-1.2332</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.9412</v>
+        <v>-1.4439</v>
       </c>
       <c r="O15" t="n">
-        <v>-0.4629</v>
+        <v>0.2107</v>
       </c>
       <c r="P15" t="n">
-        <v>0.616</v>
+        <v>-0.4107</v>
       </c>
       <c r="Q15" t="n">
-        <v>-1.0267</v>
+        <v>-1.2321</v>
       </c>
       <c r="R15" t="n">
-        <v>1.6427</v>
+        <v>0.8214</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.1524</v>
+        <v>-0.0387</v>
       </c>
       <c r="T15" t="n">
-        <v>0.4144</v>
+        <v>-0.2132</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.5667</v>
+        <v>0.1744</v>
       </c>
       <c r="V15" t="n">
-        <v>1.4189</v>
+        <v>0.3491</v>
       </c>
       <c r="W15" t="n">
-        <v>1.4189</v>
+        <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>0</v>
+        <v>0.3491</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>H. FIGUEROA ÁLVAREZ</t>
+          <t>A. SMITH</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>0.4186</v>
+        <v>0.4915</v>
       </c>
       <c r="E16" t="n">
-        <v>1.5342</v>
+        <v>0.6121</v>
       </c>
       <c r="F16" t="n">
-        <v>-1.1156</v>
+        <v>-0.1206</v>
       </c>
       <c r="G16" t="n">
-        <v>0.09669999999999999</v>
+        <v>-1.2847</v>
       </c>
       <c r="H16" t="n">
-        <v>1.7389</v>
+        <v>-0.7294</v>
       </c>
       <c r="I16" t="n">
-        <v>-1.6422</v>
+        <v>-0.5552</v>
       </c>
       <c r="J16" t="n">
-        <v>2.7345</v>
+        <v>0.1194</v>
       </c>
       <c r="K16" t="n">
-        <v>2.9851</v>
+        <v>0.2117</v>
       </c>
       <c r="L16" t="n">
-        <v>-0.2506</v>
+        <v>-0.09229999999999999</v>
       </c>
       <c r="M16" t="n">
-        <v>-2.6379</v>
+        <v>-1.4041</v>
       </c>
       <c r="N16" t="n">
-        <v>-1.2462</v>
+        <v>-0.9412</v>
       </c>
       <c r="O16" t="n">
-        <v>-1.3917</v>
+        <v>-0.4629</v>
       </c>
       <c r="P16" t="n">
-        <v>-0</v>
+        <v>0.616</v>
       </c>
       <c r="Q16" t="n">
-        <v>-2.0534</v>
+        <v>-1.0267</v>
       </c>
       <c r="R16" t="n">
-        <v>2.0534</v>
+        <v>1.6427</v>
       </c>
       <c r="S16" t="n">
-        <v>-1.0969</v>
+        <v>-0.2587</v>
       </c>
       <c r="T16" t="n">
-        <v>-1.0462</v>
+        <v>0.1005</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.0507</v>
+        <v>-0.3593</v>
       </c>
       <c r="V16" t="n">
         <v>1.4189</v>
       </c>
       <c r="W16" t="n">
-        <v>1.8993</v>
+        <v>1.4189</v>
       </c>
       <c r="X16" t="n">
-        <v>-0.4805</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>O. THIAM PEDRERA</t>
+          <t>G. VAZQUEZ VALLEJO</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,67 +1735,67 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.1698</v>
+        <v>-0.1584</v>
       </c>
       <c r="E17" t="n">
-        <v>0.3161</v>
+        <v>0.7000999999999999</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.1463</v>
+        <v>-0.8585</v>
       </c>
       <c r="G17" t="n">
-        <v>0.8419</v>
+        <v>0.8045</v>
       </c>
       <c r="H17" t="n">
-        <v>-1.421</v>
+        <v>0.8467</v>
       </c>
       <c r="I17" t="n">
-        <v>2.263</v>
+        <v>-0.0421</v>
       </c>
       <c r="J17" t="n">
-        <v>2.0751</v>
+        <v>3.3581</v>
       </c>
       <c r="K17" t="n">
-        <v>0.0229</v>
+        <v>2.1481</v>
       </c>
       <c r="L17" t="n">
-        <v>2.0522</v>
+        <v>1.21</v>
       </c>
       <c r="M17" t="n">
-        <v>-1.2332</v>
+        <v>-2.5536</v>
       </c>
       <c r="N17" t="n">
-        <v>-1.4439</v>
+        <v>-1.3014</v>
       </c>
       <c r="O17" t="n">
-        <v>0.2107</v>
+        <v>-1.2522</v>
       </c>
       <c r="P17" t="n">
-        <v>-0.4107</v>
+        <v>-1.0267</v>
       </c>
       <c r="Q17" t="n">
-        <v>-1.2321</v>
+        <v>-3.0801</v>
       </c>
       <c r="R17" t="n">
-        <v>0.8214</v>
+        <v>2.0534</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.6106</v>
+        <v>0.7845</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.527</v>
+        <v>0.1819</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.08359999999999999</v>
+        <v>0.6026</v>
       </c>
       <c r="V17" t="n">
-        <v>0.3491</v>
+        <v>-0.7207</v>
       </c>
       <c r="W17" t="n">
-        <v>0</v>
+        <v>0.2402</v>
       </c>
       <c r="X17" t="n">
-        <v>0.3491</v>
+        <v>-0.9609</v>
       </c>
     </row>
     <row r="18">
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-1.0085</v>
+        <v>-0.7365</v>
       </c>
       <c r="E18" t="n">
-        <v>0.6915</v>
+        <v>0.5869</v>
       </c>
       <c r="F18" t="n">
-        <v>-1.7</v>
+        <v>-1.3234</v>
       </c>
       <c r="G18" t="n">
         <v>0.1942</v>
@@ -1858,13 +1858,13 @@
         <v>1.2321</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.0241</v>
+        <v>0.2479</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.0931</v>
+        <v>-0.1977</v>
       </c>
       <c r="U18" t="n">
-        <v>0.06900000000000001</v>
+        <v>0.4457</v>
       </c>
       <c r="V18" t="n">
         <v>-1.1786</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-2.7384</v>
+        <v>-2.3148</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.4886</v>
+        <v>-0.1748</v>
       </c>
       <c r="F19" t="n">
-        <v>-2.2499</v>
+        <v>-2.1401</v>
       </c>
       <c r="G19" t="n">
         <v>-1.1995</v>
@@ -1936,13 +1936,13 @@
         <v>0.4107</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.0934</v>
+        <v>0.3303</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.5928</v>
+        <v>-0.279</v>
       </c>
       <c r="U19" t="n">
-        <v>0.4995</v>
+        <v>0.6093</v>
       </c>
       <c r="V19" t="n">
         <v>-0.8295</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-3.154</v>
+        <v>-2.9291</v>
       </c>
       <c r="E20" t="n">
-        <v>-3.1101</v>
+        <v>-2.7963</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.0438</v>
+        <v>-0.1328</v>
       </c>
       <c r="G20" t="n">
         <v>-0.9599</v>
@@ -2014,13 +2014,13 @@
         <v>0.8214</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.7566000000000001</v>
+        <v>-0.5318000000000001</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.7905</v>
+        <v>-0.4767</v>
       </c>
       <c r="U20" t="n">
-        <v>0.0338</v>
+        <v>-0.0551</v>
       </c>
       <c r="V20" t="n">
         <v>0</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-3.5347</v>
+        <v>-3.3691</v>
       </c>
       <c r="E21" t="n">
-        <v>-1.7492</v>
+        <v>-1.4354</v>
       </c>
       <c r="F21" t="n">
-        <v>-1.7854</v>
+        <v>-1.9336</v>
       </c>
       <c r="G21" t="n">
         <v>-0.4518</v>
@@ -2092,13 +2092,13 @@
         <v>1.0267</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.8774999999999999</v>
+        <v>-0.7119</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.5928</v>
+        <v>-0.279</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.2846</v>
+        <v>-0.4328</v>
       </c>
       <c r="V21" t="n">
         <v>-1.1786</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-4.3961</v>
+        <v>-4.2305</v>
       </c>
       <c r="E22" t="n">
-        <v>-4.5727</v>
+        <v>-4.2589</v>
       </c>
       <c r="F22" t="n">
-        <v>0.1766</v>
+        <v>0.0284</v>
       </c>
       <c r="G22" t="n">
         <v>-2.6805</v>
@@ -2170,13 +2170,13 @@
         <v>2.2588</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.4282</v>
+        <v>-0.2626</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.8758</v>
+        <v>-0.5620000000000001</v>
       </c>
       <c r="U22" t="n">
-        <v>0.4477</v>
+        <v>0.2995</v>
       </c>
       <c r="V22" t="n">
         <v>-1.2875</v>
@@ -2203,28 +2203,28 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-9.074300000000001</v>
+        <v>-8.272400000000001</v>
       </c>
       <c r="E23" t="n">
-        <v>-3.1676</v>
+        <v>-3.062999999999999</v>
       </c>
       <c r="F23" t="n">
-        <v>-5.9066</v>
+        <v>-5.209299999999999</v>
       </c>
       <c r="G23" t="n">
         <v>-3.3146</v>
       </c>
       <c r="H23" t="n">
-        <v>-4.5903</v>
+        <v>-4.590300000000001</v>
       </c>
       <c r="I23" t="n">
-        <v>1.276100000000001</v>
+        <v>1.2761</v>
       </c>
       <c r="J23" t="n">
         <v>13.3967</v>
       </c>
       <c r="K23" t="n">
-        <v>6.215999999999999</v>
+        <v>6.216</v>
       </c>
       <c r="L23" t="n">
         <v>7.1805</v>
@@ -2236,7 +2236,7 @@
         <v>-10.8067</v>
       </c>
       <c r="O23" t="n">
-        <v>-5.9047</v>
+        <v>-5.904699999999999</v>
       </c>
       <c r="P23" t="n">
         <v>-3.0801</v>
@@ -2248,13 +2248,13 @@
         <v>14.374</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.2136000000000006</v>
+        <v>0.5885000000000002</v>
       </c>
       <c r="T23" t="n">
-        <v>-1.5124</v>
+        <v>-1.4079</v>
       </c>
       <c r="U23" t="n">
-        <v>1.2991</v>
+        <v>1.9965</v>
       </c>
       <c r="V23" t="n">
         <v>-2.4659</v>
@@ -2263,7 +2263,7 @@
         <v>2.4023</v>
       </c>
       <c r="X23" t="n">
-        <v>-4.868300000000001</v>
+        <v>-4.8683</v>
       </c>
     </row>
   </sheetData>
